--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="266">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,9 +781,6 @@
   </si>
   <si>
     <t>Coded representation of the qualification.</t>
-  </si>
-  <si>
-    <t>Specific qualification the practitioner has to provide a service.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
@@ -1180,7 +1177,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="58.06640625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="53.953125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -3896,11 +3893,9 @@
       <c r="X24" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -3939,7 +3934,7 @@
         <v>219</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -3947,10 +3942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3973,17 +3968,17 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4032,7 +4027,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4050,10 +4045,10 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>76</v>
@@ -4061,10 +4056,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4087,13 +4082,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4144,7 +4139,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4162,7 +4157,7 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
@@ -4173,10 +4168,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4202,16 +4197,16 @@
         <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4260,7 +4255,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4275,13 +4270,13 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
